--- a/output/pdf_financials_xlsx/NBRK.xlsx
+++ b/output/pdf_financials_xlsx/NBRK.xlsx
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006994</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001523</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006673</v>
       </c>
     </row>
     <row r="13">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.034488</v>
+        <v>-1.041482</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.809229</v>
+        <v>-0.810752</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.791131</v>
+        <v>-0.797804</v>
       </c>
     </row>
     <row r="28">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.034488</v>
+        <v>-1.041482</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.809229</v>
+        <v>-0.810752</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.791131</v>
+        <v>-0.797804</v>
       </c>
     </row>
     <row r="30">
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.212205</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037548</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.607074</v>
       </c>
     </row>
     <row r="35">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.212205</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.037548</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.607074</v>
       </c>
     </row>
     <row r="37">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.422131</v>
+        <v>0.209926</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.244513</v>
+        <v>0.206965</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.161476</v>
+        <v>1.554402</v>
       </c>
     </row>
     <row r="49">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/NBRK.xlsx
+++ b/output/pdf_financials_xlsx/NBRK.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.235917</v>
+        <v>0.385917</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.119713</v>
+        <v>0.266213</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.105469</v>
+        <v>0.213469</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.235917</v>
+        <v>0.385917</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.119713</v>
+        <v>0.266213</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.105469</v>
+        <v>0.213469</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.119713</v>
+        <v>-0.266213</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.105469</v>
+        <v>-0.213469</v>
       </c>
     </row>
     <row r="12">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.191225</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.186597</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="38">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.022337</v>
+        <v>0.213562</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.05831</v>
+        <v>0.244907</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.128203</v>
+        <v>0.329203</v>
       </c>
     </row>
     <row r="42">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.209926</v>
+        <v>0.018701</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.206965</v>
+        <v>0.020368</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.554402</v>
+        <v>1.353402</v>
       </c>
     </row>
     <row r="49">
@@ -1243,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>1.326</v>
       </c>
     </row>
     <row r="51">
@@ -1425,10 +1425,10 @@
         <v>0.543</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.543</v>
+        <v>0.535</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.7355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.00047</v>
       </c>
     </row>
     <row r="116">
@@ -2765,7 +2765,11 @@
           <t>Other amounts receivable Notes 7,14</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -2825,7 +2829,11 @@
           <t>Investments Note 6</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -2885,7 +2893,11 @@
           <t>Mineral properties Note 7</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.543</v>
       </c>
@@ -3210,7 +3222,11 @@
           <t>Other amounts receivable Notes 7, 14</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.191225</v>
       </c>
@@ -3239,7 +3255,11 @@
           <t>Investment Note 6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3448,7 +3468,11 @@
           <t>Realized loss on sale of investment Note 7</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -3715,7 +3739,11 @@
           <t>Proceeds on sale of investment Note 6</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4402,7 +4430,11 @@
           <t>Management fees Note 10</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.15</v>
       </c>

--- a/output/pdf_financials_xlsx/NBRK.xlsx
+++ b/output/pdf_financials_xlsx/NBRK.xlsx
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.051225</v>
+        <v>-0.034713</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.005628</v>
+        <v>-0.030345</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.014403</v>
+        <v>-0.084296</v>
       </c>
     </row>
     <row r="102">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.174669</v>
+        <v>0.191181</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.100278</v>
+        <v>0.064305</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.14511</v>
+        <v>-0.215003</v>
       </c>
     </row>
     <row r="107">
@@ -3559,7 +3559,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.016512</v>
       </c>
